--- a/server/data/clients.xlsx
+++ b/server/data/clients.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ngel235\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD485C27-97B9-41B0-8737-151CD70A979B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE8AD5E7-7DC2-4FF8-9412-CA14F1091B6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-2070" windowWidth="29040" windowHeight="15720" xr2:uid="{5F9440D5-75FF-4BD3-BD7A-55E9B769873D}"/>
+    <workbookView xWindow="-28920" yWindow="-2070" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{5F9440D5-75FF-4BD3-BD7A-55E9B769873D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="1st Batch" sheetId="1" r:id="rId1"/>
+    <sheet name="2nd Batch" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3899" uniqueCount="1523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5438" uniqueCount="1712">
   <si>
     <t>Public Wifi Project</t>
   </si>
@@ -4608,6 +4609,573 @@
   </si>
   <si>
     <t>it@marijanihotel.co.tz</t>
+  </si>
+  <si>
+    <t>Recurring service price</t>
+  </si>
+  <si>
+    <t>Manual Billing</t>
+  </si>
+  <si>
+    <t>Estim Enterprises Limited</t>
+  </si>
+  <si>
+    <t>DIA 12M Burst 14, Office Serereka 25Mb, DIA 5M Burst 7M, DIA 5M Burst 7M, DIA 20M</t>
+  </si>
+  <si>
+    <t>Fumba 2</t>
+  </si>
+  <si>
+    <t>n.umaraniya@estimconstruction.com</t>
+  </si>
+  <si>
+    <t>Shakani</t>
+  </si>
+  <si>
+    <t>Shakani, Airport, TCRA, Kisauni, kiwengwa</t>
+  </si>
+  <si>
+    <t>CRJE (East Africa Limited) - Bweleo Factory</t>
+  </si>
+  <si>
+    <t>aminakombo415@yahoo.com</t>
+  </si>
+  <si>
+    <t>Bweleo</t>
+  </si>
+  <si>
+    <t>Union Property Developers - Mzee Villa</t>
+  </si>
+  <si>
+    <t>Delphi A1 Limited</t>
+  </si>
+  <si>
+    <t>stephanie.amerman@toc.co.tz</t>
+  </si>
+  <si>
+    <t>Nyamanzi</t>
+  </si>
+  <si>
+    <t>Ali Hassan | Calamari Beach Villa</t>
+  </si>
+  <si>
+    <t>calamari_znz@yahoo.com</t>
+  </si>
+  <si>
+    <t>Fisherman Tours &amp; Travel - Kombeni House</t>
+  </si>
+  <si>
+    <t>Entertainment 7Mb-10Mb</t>
+  </si>
+  <si>
+    <t>salum@fishermantours.com</t>
+  </si>
+  <si>
+    <t>Kombeni</t>
+  </si>
+  <si>
+    <t>Mohamed Juma Shaaban</t>
+  </si>
+  <si>
+    <t>mjshaaban@gmail.com</t>
+  </si>
+  <si>
+    <t>shakani</t>
+  </si>
+  <si>
+    <t>Fumba Lodge / Swahili house</t>
+  </si>
+  <si>
+    <t>Home Pack Lite 3-5 Mb, Pwani Breeze - 30M Burst 33M, Zanzi Lite - 10M Burst 12M</t>
+  </si>
+  <si>
+    <t>manager@fumbabeachlodge.co.tz</t>
+  </si>
+  <si>
+    <t>Fumba uptown</t>
+  </si>
+  <si>
+    <t>Edwin Home, Fumba Lodge, Swahili - Mchamba wima</t>
+  </si>
+  <si>
+    <t>Alfredo Store Limited</t>
+  </si>
+  <si>
+    <t>sales@alfredoestore.com</t>
+  </si>
+  <si>
+    <t>TMA Holdings Company Limited</t>
+  </si>
+  <si>
+    <t>accountant@zanzibarwaterfront.com</t>
+  </si>
+  <si>
+    <t>Zanzibar Feza Schools</t>
+  </si>
+  <si>
+    <t>fezazanzibar@fezaschools.org</t>
+  </si>
+  <si>
+    <t>Tabasam Group</t>
+  </si>
+  <si>
+    <t>Wakawaka 50Mb 10M, DIA 80M, DIA 40M</t>
+  </si>
+  <si>
+    <t>info@tabasamtours.com</t>
+  </si>
+  <si>
+    <t>Radius British School, Trymedics Mbweni - Chuo cha Afya, Migomban</t>
+  </si>
+  <si>
+    <t>Al-Hussein Construction Limited | Bweleo</t>
+  </si>
+  <si>
+    <t>aliasgerdossaji.ahc@gmail.com</t>
+  </si>
+  <si>
+    <t>Yasser Provission Store Limited</t>
+  </si>
+  <si>
+    <t>Dnata Zanzibar Aviation Service Company Limited</t>
+  </si>
+  <si>
+    <t>DIA 120M, Entertainment 7Mb-10Mb</t>
+  </si>
+  <si>
+    <t>Euro World Travel Services Ltd</t>
+  </si>
+  <si>
+    <t>ashish.tilwani@satgurutravel.com</t>
+  </si>
+  <si>
+    <t>Sama Hospitality Supplies Limited- Production</t>
+  </si>
+  <si>
+    <t>Zanzibar Aviation Services</t>
+  </si>
+  <si>
+    <t>DIA 2M Burst 4M, DIA 3M Burst 5M, DIA 20M, Kahawa Surf - 20M Burst 22M</t>
+  </si>
+  <si>
+    <t>finance@zat.co.tz</t>
+  </si>
+  <si>
+    <t>airport</t>
+  </si>
+  <si>
+    <t>Royal Securities, Hassan Raza Workshop, ZAT Airport, Hassan Raza Home</t>
+  </si>
+  <si>
+    <t>Zanzibar Investment Summit2026</t>
+  </si>
+  <si>
+    <t>DIA 300M</t>
+  </si>
+  <si>
+    <t>Golden Tulip Airport</t>
+  </si>
+  <si>
+    <t>Mkwawa Construction (Z) Limited</t>
+  </si>
+  <si>
+    <t>irespicius@Mkwawa-LC.com</t>
+  </si>
+  <si>
+    <t>Maisara</t>
+  </si>
+  <si>
+    <t>Zan-container Solution Ltd</t>
+  </si>
+  <si>
+    <t>ibrahim@zikanet.co.tz</t>
+  </si>
+  <si>
+    <t>Community Forest Pemba</t>
+  </si>
+  <si>
+    <t>eric@forestsinternational.org</t>
+  </si>
+  <si>
+    <t>GPC Limited (Pongwe Bay Resort)</t>
+  </si>
+  <si>
+    <t>stefanocolombino.ss@gmail.com</t>
+  </si>
+  <si>
+    <t>ZMS Company Limited (Bellimena)</t>
+  </si>
+  <si>
+    <t>mohamed.kassongo@gmail.com</t>
+  </si>
+  <si>
+    <t>Hurumzi</t>
+  </si>
+  <si>
+    <t>The 5th Element Boutique Hotel</t>
+  </si>
+  <si>
+    <t>zanyumba2025@gmail.com</t>
+  </si>
+  <si>
+    <t>One Planet Hospitality Limited</t>
+  </si>
+  <si>
+    <t>amishev93@gmail.com</t>
+  </si>
+  <si>
+    <t>Paje (Heart of Zanzibar)</t>
+  </si>
+  <si>
+    <t>Paje Cave Company Limited</t>
+  </si>
+  <si>
+    <t>kisinsimon@gmail.com</t>
+  </si>
+  <si>
+    <t>Protels Hotel &amp; Resort LImited</t>
+  </si>
+  <si>
+    <t>gm.laplage@protels.com</t>
+  </si>
+  <si>
+    <t>Shanka Zanzibar Limited</t>
+  </si>
+  <si>
+    <t>shanka.music@gmail.com</t>
+  </si>
+  <si>
+    <t>Kizimkazi</t>
+  </si>
+  <si>
+    <t>Sun Gym Zanzibar Limited</t>
+  </si>
+  <si>
+    <t>Tanzanite Beach Resort - Maruhubi</t>
+  </si>
+  <si>
+    <t>saltanzanite@gmail.com</t>
+  </si>
+  <si>
+    <t>Bakery Pride Bakery</t>
+  </si>
+  <si>
+    <t>bakersprideznz@gmail.com</t>
+  </si>
+  <si>
+    <t>Vuga</t>
+  </si>
+  <si>
+    <t>Breezes Director Home</t>
+  </si>
+  <si>
+    <t>CPS Staff temporary connection</t>
+  </si>
+  <si>
+    <t>juma.doho@liquidtech.co.tz</t>
+  </si>
+  <si>
+    <t>Kwetu Kwenu Market -Test 1</t>
+  </si>
+  <si>
+    <t>busara@busara.or.tz</t>
+  </si>
+  <si>
+    <t>Kwetu Kwenu Chill Test 2</t>
+  </si>
+  <si>
+    <t>3TK &amp; Bunam Foodstuff Co. LTD</t>
+  </si>
+  <si>
+    <t>Masingini</t>
+  </si>
+  <si>
+    <t>kkwaza01@gmail.com</t>
+  </si>
+  <si>
+    <t>Amani</t>
+  </si>
+  <si>
+    <t>Ak Colour Station (Kianga)</t>
+  </si>
+  <si>
+    <t>Kianga</t>
+  </si>
+  <si>
+    <t>Mahmoud Alawi - Site 2</t>
+  </si>
+  <si>
+    <t>mudyalawi@gmail.com</t>
+  </si>
+  <si>
+    <t>Asha Ali Yahya</t>
+  </si>
+  <si>
+    <t>Home Essential 5Mb</t>
+  </si>
+  <si>
+    <t>hassvy2025@gmail.com</t>
+  </si>
+  <si>
+    <t>Fuoni Meli Nne</t>
+  </si>
+  <si>
+    <t>Basra Textile Mills Ltd</t>
+  </si>
+  <si>
+    <t>aliidrissai54@gmail.com</t>
+  </si>
+  <si>
+    <t>Mwembe Makumbi</t>
+  </si>
+  <si>
+    <t>Burhan - Zanzibar Food &amp; Drug Agent Free with ZFDA</t>
+  </si>
+  <si>
+    <t>bsimai@yahoo.com</t>
+  </si>
+  <si>
+    <t>Changuu Lodge Limited</t>
+  </si>
+  <si>
+    <t>Changuu Island</t>
+  </si>
+  <si>
+    <t>China Railway Construction Engineering Group Co. LTD (CRCEG)</t>
+  </si>
+  <si>
+    <t>zhaoyufeng@crceg-int.com</t>
+  </si>
+  <si>
+    <t>Kisakasaka</t>
+  </si>
+  <si>
+    <t>Gong Yuhai</t>
+  </si>
+  <si>
+    <t>lyugino671@gmail.com</t>
+  </si>
+  <si>
+    <t>Salum Hassan</t>
+  </si>
+  <si>
+    <t>sadi75413@gmail.com</t>
+  </si>
+  <si>
+    <t>Irvines Tanzania Limited</t>
+  </si>
+  <si>
+    <t>adolph@irvines.co.tz</t>
+  </si>
+  <si>
+    <t>Amani Stadium</t>
+  </si>
+  <si>
+    <t>Jacob Makundi</t>
+  </si>
+  <si>
+    <t>g-manager@oceangrouphotel.com</t>
+  </si>
+  <si>
+    <t>Jakub Wizor</t>
+  </si>
+  <si>
+    <t>servicezanzibar@gmail.com</t>
+  </si>
+  <si>
+    <t>Jamal Nassor Said - Fuoni</t>
+  </si>
+  <si>
+    <t>jamalsaid@gmail.com</t>
+  </si>
+  <si>
+    <t>Jessica Tareto Peter</t>
+  </si>
+  <si>
+    <t>peterjessica8515@gmail.com</t>
+  </si>
+  <si>
+    <t>Kiponda</t>
+  </si>
+  <si>
+    <t>Iris Aser JV Limited - Kibele</t>
+  </si>
+  <si>
+    <t>DIA 180M</t>
+  </si>
+  <si>
+    <t>Kibele</t>
+  </si>
+  <si>
+    <t>Saleh Hassan Makame</t>
+  </si>
+  <si>
+    <t>bifety903@gmail.com</t>
+  </si>
+  <si>
+    <t>Mariam Amour Mwinyi</t>
+  </si>
+  <si>
+    <t>mwinyi.maryam@gmail.com</t>
+  </si>
+  <si>
+    <t>Mbaruku Khamis Mbaruku</t>
+  </si>
+  <si>
+    <t>mkmbaruk@gmail.com</t>
+  </si>
+  <si>
+    <t>Mwera</t>
+  </si>
+  <si>
+    <t>Mwinyi Haji Ramadhan</t>
+  </si>
+  <si>
+    <t>binmwinyi@yandex.com</t>
+  </si>
+  <si>
+    <t>Fuoni Mtundani</t>
+  </si>
+  <si>
+    <t>Rashid Mzee Abdalla-Jumbi</t>
+  </si>
+  <si>
+    <t>abby0012005@yahoo.com</t>
+  </si>
+  <si>
+    <t>Jumbi</t>
+  </si>
+  <si>
+    <t>Green Telecom (Oman Consulate)</t>
+  </si>
+  <si>
+    <t>kariakoo</t>
+  </si>
+  <si>
+    <t>Omar Said Shaaban2</t>
+  </si>
+  <si>
+    <t>omary@saidattorneys.com</t>
+  </si>
+  <si>
+    <t>Kwerekwe</t>
+  </si>
+  <si>
+    <t>Prime Regional Supplies Limited</t>
+  </si>
+  <si>
+    <t>salehe.muguzi@Lubejunction.com</t>
+  </si>
+  <si>
+    <t>Kibweni</t>
+  </si>
+  <si>
+    <t>Source Link Limited</t>
+  </si>
+  <si>
+    <t>sourcelinkltd@gmail.com</t>
+  </si>
+  <si>
+    <t>Kwa Nyanya</t>
+  </si>
+  <si>
+    <t>Suleiman Abdalla Suleiman</t>
+  </si>
+  <si>
+    <t>almaulys@yahoo.com</t>
+  </si>
+  <si>
+    <t>Two Brothers Tours Partnership (Home)</t>
+  </si>
+  <si>
+    <t>twobrotherstourszanzi@gmail.com</t>
+  </si>
+  <si>
+    <t>Vishal Shantilal</t>
+  </si>
+  <si>
+    <t>vishalstulsi@gmail.com</t>
+  </si>
+  <si>
+    <t>Z-Summit event</t>
+  </si>
+  <si>
+    <t>Zanzibar Cancer Association CSR</t>
+  </si>
+  <si>
+    <t>info@z-ncda.org</t>
+  </si>
+  <si>
+    <t>Mohammed Said Khamis</t>
+  </si>
+  <si>
+    <t>saeydmarine@gmail.com</t>
+  </si>
+  <si>
+    <t>Zuwena Abdulla Aziz1</t>
+  </si>
+  <si>
+    <t>saljabry11@gmail.com</t>
+  </si>
+  <si>
+    <t>Eveha East Africa</t>
+  </si>
+  <si>
+    <t>Paje 2</t>
+  </si>
+  <si>
+    <t>joseph.kovacik@eveha.fr</t>
+  </si>
+  <si>
+    <t>Lilian Heinrich Kimwerli</t>
+  </si>
+  <si>
+    <t>sembuamd@gmail.com</t>
+  </si>
+  <si>
+    <t>Hym Global Company</t>
+  </si>
+  <si>
+    <t>DIA 15M Burst 17, DIA 15M Burst 17, DIA 15M Burst 17, DIA 15M Burst 17</t>
+  </si>
+  <si>
+    <t>Iasmina Onescu</t>
+  </si>
+  <si>
+    <t>33 629 80 39 61</t>
+  </si>
+  <si>
+    <t>kilimavillas@coldwellbanker.tz</t>
+  </si>
+  <si>
+    <t>Lulu Apartments (Bhadra Clobal Ventures Limited)</t>
+  </si>
+  <si>
+    <t>sarunassaltis@yahoo.co.uk</t>
+  </si>
+  <si>
+    <t>Mbm Toursim Co Ltd (Paje Plaza Commerical Center)</t>
+  </si>
+  <si>
+    <t>zenobiazanzibar@gmail.com</t>
+  </si>
+  <si>
+    <t>Samawa Resort 2</t>
+  </si>
+  <si>
+    <t>engineering@samawazanzibar.com</t>
+  </si>
+  <si>
+    <t>Sharazad Boutique Hotel (Seaside LTD)</t>
+  </si>
+  <si>
+    <t>DIA 10M Burst 20M, DIA 50M</t>
+  </si>
+  <si>
+    <t>gm@sharazadboutiquehotel.com</t>
+  </si>
+  <si>
+    <t>Town Connection, Jambiani Hotel</t>
   </si>
 </sst>
 </file>
@@ -20244,6 +20812,6183 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82538E0A-DFBD-4C7B-9950-BB30B474C2DF}">
+  <dimension ref="B2:L320"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="16.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B2" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>1523</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>1524</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B3" s="1" t="s">
+        <v>1525</v>
+      </c>
+      <c r="C3" s="1">
+        <v>255746941928</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>1526</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1" t="s">
+        <v>1527</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>1528</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>1529</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>1530</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
+        <v>1531</v>
+      </c>
+      <c r="C4" s="1">
+        <v>255765104623</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1" t="s">
+        <v>1527</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>1532</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>1533</v>
+      </c>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B5" s="1" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C5" s="1">
+        <v>255715307766</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1" t="s">
+        <v>1527</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C6" s="1">
+        <v>773332133</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1" t="s">
+        <v>1527</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>1536</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>1537</v>
+      </c>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="1" t="s">
+        <v>1538</v>
+      </c>
+      <c r="C7" s="1">
+        <v>255672129317</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1" t="s">
+        <v>1527</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>1539</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>1533</v>
+      </c>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B8" s="1" t="s">
+        <v>1540</v>
+      </c>
+      <c r="C8" s="1">
+        <v>255774230043</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>1541</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1" t="s">
+        <v>1527</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>1542</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>1543</v>
+      </c>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B9" s="1" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C9" s="1">
+        <v>255779039154</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>1541</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1" t="s">
+        <v>1527</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>1545</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>1546</v>
+      </c>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B10" s="1" t="s">
+        <v>1547</v>
+      </c>
+      <c r="C10" s="1">
+        <v>255777703339</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>1548</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1" t="s">
+        <v>1527</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>1549</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>1550</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>1551</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B11" s="1" t="s">
+        <v>1552</v>
+      </c>
+      <c r="C11" s="1">
+        <v>255757455410</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1" t="s">
+        <v>1527</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>1553</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>1533</v>
+      </c>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B12" s="1" t="s">
+        <v>1554</v>
+      </c>
+      <c r="C12" s="1">
+        <v>255776436693</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1" t="s">
+        <v>1527</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>1555</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>1533</v>
+      </c>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>1556</v>
+      </c>
+      <c r="C13" s="1">
+        <v>255777869414</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1" t="s">
+        <v>1527</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>1557</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B14" s="1" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C14" s="1">
+        <v>255777413585</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>1559</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1" t="s">
+        <v>1527</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>1560</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>1561</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B15" s="1" t="s">
+        <v>1562</v>
+      </c>
+      <c r="C15" s="1">
+        <v>255776794833</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1" t="s">
+        <v>1527</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>1563</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>1533</v>
+      </c>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B16" s="1" t="s">
+        <v>1564</v>
+      </c>
+      <c r="C16" s="1">
+        <v>255718585282</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1" t="s">
+        <v>1527</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B18" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="C18" s="1">
+        <v>255773343805</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>1566</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" s="1"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B19" s="1" t="s">
+        <v>1567</v>
+      </c>
+      <c r="C19" s="1">
+        <v>255759377229</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>1568</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H19" s="1"/>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B20" s="1" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C20" s="1">
+        <v>255652656590</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B21" s="1" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C21" s="1">
+        <v>255773660733</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>1571</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>1572</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>1573</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B22" s="1" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C22" s="1">
+        <v>255657390956</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1" t="s">
+        <v>1577</v>
+      </c>
+      <c r="H22" s="1"/>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B25" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="C25" s="1">
+        <v>255778664546</v>
+      </c>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B26" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B27" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="C27" s="1">
+        <v>255620481082</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B28" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="C28" s="1">
+        <v>255777879066</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B29" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="C29" s="1">
+        <v>255777478527</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B30" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="C30" s="1">
+        <v>2255763381488</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B33" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="C33" s="1">
+        <v>255772830853</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B34" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="C34" s="1">
+        <v>255757962590</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B35" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="C35" s="1">
+        <v>255786777722</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B36" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="C36" s="1">
+        <v>255623557426</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B37" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="C37" s="1">
+        <v>255777701338</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B40" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="C40" s="1">
+        <v>255715279728</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B41" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="C41" s="1">
+        <v>255777439655</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B42" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="C42" s="1">
+        <v>255682057708</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B43" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="C43" s="1">
+        <v>255786761031</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B46" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B47" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B48" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="C48" s="1">
+        <v>255719802062</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B49" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="C49" s="1">
+        <v>255776055807</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B50" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="C50" s="1">
+        <v>255655814121</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B51" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="C51" s="1">
+        <v>255773332133</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B52" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="C52" s="1">
+        <v>255621757580</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B53" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="C53" s="1">
+        <v>255621852915</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B54" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="C54" s="1">
+        <v>255777328019</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="G54" s="1"/>
+    </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B55" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="C55" s="1">
+        <v>255658194446</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B56" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="C56" s="1">
+        <v>255747439784</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="G56" s="1"/>
+    </row>
+    <row r="57" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B57" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="C57" s="1">
+        <v>255776055807</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B60" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B61" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C61" s="1">
+        <v>2552250719</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B62" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C62" s="1">
+        <v>255713112518</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B63" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C63" s="1">
+        <v>255777411550</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B64" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C64" s="1">
+        <v>255775000006</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B65" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C65" s="1">
+        <v>255777411023</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="66" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B66" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C66" s="1">
+        <v>255777478800</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B67" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C67" s="1">
+        <v>255757807920</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="68" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B68" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C68" s="1">
+        <v>255776448081</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="69" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B69" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C69" s="1">
+        <v>255777488888</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B70" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C70" s="1">
+        <v>255689684488</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="71" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B71" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C71" s="1">
+        <v>255777493094</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B72" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C72" s="1">
+        <v>255682024994</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="73" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B73" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C73" s="1">
+        <v>255655400812</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="74" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B74" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C74" s="1">
+        <v>255777411142</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="75" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B75" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C75" s="1">
+        <v>255772187580</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="76" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B76" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C76" s="1">
+        <v>255621023306</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="77" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B77" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C77" s="1">
+        <v>255679342824</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="78" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B78" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C78" s="1">
+        <v>255777535952</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="79" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B79" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C79" s="1">
+        <v>255772100023</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="80" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B80" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C80" s="1">
+        <v>255716296405</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="81" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B81" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C81" s="1">
+        <v>255772761876</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="82" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B82" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C82" s="1">
+        <v>255777946566</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="83" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B83" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C83" s="1">
+        <v>255778670087</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="84" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B84" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C84" s="1">
+        <v>255621102448</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="85" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B85" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C85" s="1">
+        <v>255777415340</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="86" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B86" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C86" s="1">
+        <v>255777490464</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="87" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B87" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C87" s="1">
+        <v>255777477053</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="88" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B88" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="C88" s="1">
+        <v>255718585282</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="89" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B89" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C89" s="1">
+        <v>255773549235</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B90" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C90" s="1">
+        <v>255715390344</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="91" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B91" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="C91" s="1">
+        <v>255777412150</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="92" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B92" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C92" s="1">
+        <v>255754855960</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="93" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B93" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C93" s="1">
+        <v>255754855960</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="94" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B94" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C94" s="1">
+        <v>255685472063</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="95" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B95" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C95" s="1">
+        <v>255777777761</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="96" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B96" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C96" s="1">
+        <v>255772686428</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="97" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B97" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C97" s="1">
+        <v>255715814421</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="98" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B98" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C98" s="1">
+        <v>255677020426</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="99" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B99" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C99" s="1">
+        <v>255682703554</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="100" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B100" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C100" s="1">
+        <v>255759817126</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="101" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B101" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C101" s="1">
+        <v>255773876820</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="102" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B102" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C102" s="1">
+        <v>255778971693</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="103" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B103" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C103" s="1">
+        <v>255776464403</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="104" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B104" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C104" s="1">
+        <v>255774307426</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="105" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B105" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C105" s="1">
+        <v>255776415066</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="106" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B106" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C106" s="1">
+        <v>255772955945</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="107" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B107" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C107" s="1">
+        <v>255778283770</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="108" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B108" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C108" s="1">
+        <v>255713301638</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="109" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B109" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="C109" s="1">
+        <v>255786230386</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="110" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B110" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C110" s="1">
+        <v>255773266255</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="111" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B111" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C111" s="1">
+        <v>255784871970</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="112" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B112" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="C112" s="1">
+        <v>255773556655</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="113" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B113" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="C113" s="1">
+        <v>255772395249</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="114" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B114" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C114" s="1">
+        <v>255777418541</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="115" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B115" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C115" s="1">
+        <v>255765571347</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="116" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B116" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="C116" s="1">
+        <v>255756429122</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="117" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B117" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="C117" s="1">
+        <v>255774688888</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="118" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B118" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C118" s="1">
+        <v>255717948907</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="119" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B119" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C119" s="1">
+        <v>255777840055</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="120" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B120" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C120" s="1">
+        <v>255716270106</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="121" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B121" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="C121" s="1">
+        <v>255654578646</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="122" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B122" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C122" s="1">
+        <v>255793770540</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="123" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B123" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C123" s="1">
+        <v>255714013944</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="124" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B124" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C124" s="1">
+        <v>255773570059</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="125" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B125" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="C125" s="1">
+        <v>255783948253</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="126" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B126" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="C126" s="1">
+        <v>255777487705</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="127" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B127" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C127" s="1">
+        <v>255772203514</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="128" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B128" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C128" s="1">
+        <v>255772251999</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="129" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B129" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C129" s="1">
+        <v>255713404442</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="130" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B130" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C130" s="1">
+        <v>255715124621</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="131" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B131" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C131" s="1">
+        <v>255777869047</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="132" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B132" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="C132" s="1">
+        <v>255622445656</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="133" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B133" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="C133" s="1">
+        <v>255752194844</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="134" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B134" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="C134" s="1">
+        <v>255656650663</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="135" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B135" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="C135" s="1">
+        <v>255773110738</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="136" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B136" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="C136" s="1">
+        <v>255655767502</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="137" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B137" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="C137" s="1">
+        <v>255777482122</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="138" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B138" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="C138" s="1">
+        <v>255777981122</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="139" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B139" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C139" s="1">
+        <v>255773099290</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="140" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B140" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="C140" s="1">
+        <v>255777478527</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="141" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B141" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C141" s="1">
+        <v>255628888885</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="142" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B142" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="C142" s="1">
+        <v>255784727476</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="143" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B143" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="C143" s="1">
+        <v>255777110035</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="144" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B144" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C144" s="1">
+        <v>255783683389</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="145" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B145" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C145" s="1">
+        <v>255776214041</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="G145" s="1" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="146" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B146" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="C146" s="1">
+        <v>255773052037</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="147" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B147" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="C147" s="1">
+        <v>255776106223</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="148" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B148" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="C148" s="1">
+        <v>255752332144</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="149" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B149" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C149" s="1">
+        <v>255778885000</v>
+      </c>
+      <c r="D149" s="1"/>
+      <c r="E149" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="150" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B150" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="C150" s="1">
+        <v>255654926560</v>
+      </c>
+      <c r="D150" s="1"/>
+      <c r="E150" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="153" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B153" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C153" s="1"/>
+      <c r="D153" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G153" s="1"/>
+    </row>
+    <row r="154" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B154" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C154" s="1">
+        <v>255714444454</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G154" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="155" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B155" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C155" s="1">
+        <v>255773047979</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G155" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="156" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B156" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C156" s="1">
+        <v>255768421196</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G156" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="157" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B157" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" s="1">
+        <v>255699563400</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G157" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="158" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B158" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C158" s="1">
+        <v>255711326709</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G158" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="159" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B159" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C159" s="1">
+        <v>255778457411</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G159" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="160" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B160" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C160" s="1">
+        <v>255777483442</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F160" s="1"/>
+      <c r="G160" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="161" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B161" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C161" s="1">
+        <v>255777946566</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G161" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="162" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B162" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C162" s="1">
+        <v>255787111771</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G162" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="163" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B163" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C163" s="1">
+        <v>255774747400</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G163" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="164" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B164" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C164" s="1">
+        <v>255777423162</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G164" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="165" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B165" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C165" s="1">
+        <v>255776731021</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G165" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="166" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B166" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C166" s="1">
+        <v>255774811116</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G166" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="167" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B167" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C167" s="1">
+        <v>255654230294</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G167" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="168" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B168" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C168" s="1">
+        <v>255657600177</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G168" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="169" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B169" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C169" s="1">
+        <v>255714871539</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G169" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="170" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B170" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C170" s="1">
+        <v>255742100050</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G170" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="171" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B171" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C171" s="1">
+        <v>255773054115</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G171" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="172" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B172" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C172" s="1">
+        <v>255776381747</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G172" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="173" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B173" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C173" s="1">
+        <v>255776381747</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G173" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="174" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B174" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C174" s="1">
+        <v>255778000777</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G174" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="175" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B175" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C175" s="1">
+        <v>255678000078</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G175" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="176" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B176" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C176" s="1">
+        <v>255673169014</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G176" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="177" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B177" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C177" s="1">
+        <v>255772224440</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G177" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="178" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B178" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C178" s="1">
+        <v>255657777777</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G178" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="179" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B179" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C179" s="1">
+        <v>255758578354</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G179" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="180" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B180" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C180" s="1">
+        <v>254729143747</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F180" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G180" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="181" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B181" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C181" s="1">
+        <v>255788949496</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G181" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="182" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B182" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C182" s="1">
+        <v>255777411108</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F182" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G182" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="183" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B183" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C183" s="1">
+        <v>255778671531</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G183" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="184" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B184" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C184" s="1">
+        <v>255777413009</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G184" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="185" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B185" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C185" s="1">
+        <v>255773915991</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="G185" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="186" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B186" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C186" s="1">
+        <v>255772422792</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G186" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="187" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B187" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C187" s="1">
+        <v>255773343805</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G187" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="188" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B188" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C188" s="1">
+        <v>255777340444</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G188" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="189" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B189" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C189" s="1">
+        <v>255685082543</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G189" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="190" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B190" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C190" s="1">
+        <v>255683585634</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G190" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="191" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B191" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C191" s="1">
+        <v>255774660099</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E191" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F191" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="G191" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="192" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B192" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C192" s="1">
+        <v>255777162626</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G192" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="193" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B193" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C193" s="1">
+        <v>255715975986</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G193" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="194" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B194" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C194" s="1">
+        <v>255772281292</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E194" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F194" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="G194" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="195" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B195" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C195" s="1">
+        <v>255718371201</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G195" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="196" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B196" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C196" s="1">
+        <v>821093472700</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E196" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F196" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G196" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="197" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B197" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C197" s="1">
+        <v>255773636504</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F197" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G197" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="198" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B198" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C198" s="1">
+        <v>255674442074</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F198" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="G198" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="199" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B199" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C199" s="1">
+        <v>255777474566</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E199" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F199" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G199" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="200" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B200" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C200" s="1">
+        <v>255774245555</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="G200" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="201" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B201" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C201" s="1">
+        <v>255715307766</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G201" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="202" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B202" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C202" s="1">
+        <v>255777417948</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G202" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="203" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B203" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C203" s="1">
+        <v>255772911129</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G203" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="204" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B204" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C204" s="1">
+        <v>255773087440</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F204" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G204" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="205" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B205" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C205" s="1">
+        <v>255779662662</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G205" s="1"/>
+    </row>
+    <row r="206" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B206" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C206" s="1">
+        <v>255714119911</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F206" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="G206" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="207" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B207" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C207" s="1">
+        <v>255718377273</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F207" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G207" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="208" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B208" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C208" s="1">
+        <v>255776888823</v>
+      </c>
+      <c r="D208" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F208" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G208" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="209" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B209" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C209" s="1">
+        <v>255678898437</v>
+      </c>
+      <c r="D209" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F209" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G209" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="210" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B210" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C210" s="1">
+        <v>255777138642</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F210" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="G210" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="211" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B211" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C211" s="1">
+        <v>255779941515</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F211" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G211" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="212" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B212" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C212" s="1">
+        <v>255774434948</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F212" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="G212" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="213" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B213" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C213" s="1">
+        <v>255774289921</v>
+      </c>
+      <c r="D213" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F213" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G213" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="214" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B214" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C214" s="1">
+        <v>255773828087</v>
+      </c>
+      <c r="D214" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E214" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F214" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G214" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="215" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B215" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C215" s="1">
+        <v>255745752552</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F215" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G215" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="216" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B216" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C216" s="1">
+        <v>255767850575</v>
+      </c>
+      <c r="D216" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E216" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F216" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="G216" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="217" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B217" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C217" s="1">
+        <v>255785737224</v>
+      </c>
+      <c r="D217" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E217" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F217" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="G217" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="218" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B218" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C218" s="1">
+        <v>255773194766</v>
+      </c>
+      <c r="D218" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F218" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G218" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="219" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B219" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C219" s="1">
+        <v>255776434804</v>
+      </c>
+      <c r="D219" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E219" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F219" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G219" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="220" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B220" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C220" s="1">
+        <v>255716345050</v>
+      </c>
+      <c r="D220" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E220" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F220" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="G220" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="221" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B221" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C221" s="1">
+        <v>255777747788</v>
+      </c>
+      <c r="D221" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E221" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F221" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G221" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="222" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B222" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C222" s="1">
+        <v>255776896177</v>
+      </c>
+      <c r="D222" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E222" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F222" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="G222" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="223" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B223" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C223" s="1">
+        <v>255782546871</v>
+      </c>
+      <c r="D223" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E223" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F223" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="G223" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="224" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B224" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C224" s="1">
+        <v>255778017429</v>
+      </c>
+      <c r="D224" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E224" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F224" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="G224" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="225" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B225" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C225" s="1">
+        <v>255657675186</v>
+      </c>
+      <c r="D225" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E225" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F225" s="1"/>
+      <c r="G225" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="226" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B226" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C226" s="1">
+        <v>255774871857</v>
+      </c>
+      <c r="D226" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E226" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F226" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="G226" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="227" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B227" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C227" s="1">
+        <v>255774208189</v>
+      </c>
+      <c r="D227" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E227" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F227" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="G227" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="228" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B228" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C228" s="1">
+        <v>255710051718</v>
+      </c>
+      <c r="D228" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E228" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F228" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="G228" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="229" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B229" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C229" s="1">
+        <v>255757334156</v>
+      </c>
+      <c r="D229" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E229" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F229" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="G229" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="230" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B230" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C230" s="1">
+        <v>255773111008</v>
+      </c>
+      <c r="D230" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E230" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F230" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G230" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="231" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B231" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C231" s="1">
+        <v>255776150106</v>
+      </c>
+      <c r="D231" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E231" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F231" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="G231" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="232" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B232" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C232" s="1">
+        <v>255777788899</v>
+      </c>
+      <c r="D232" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E232" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F232" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G232" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="233" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B233" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C233" s="1">
+        <v>255788094586</v>
+      </c>
+      <c r="D233" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E233" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F233" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G233" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="234" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B234" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C234" s="1">
+        <v>255745844976</v>
+      </c>
+      <c r="D234" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E234" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F234" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="G234" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="235" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B235" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C235" s="1">
+        <v>255687290517</v>
+      </c>
+      <c r="D235" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E235" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F235" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="G235" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="236" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B236" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C236" s="1">
+        <v>255652098558</v>
+      </c>
+      <c r="D236" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E236" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F236" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="G236" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="237" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B237" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C237" s="1">
+        <v>255625880419</v>
+      </c>
+      <c r="D237" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E237" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F237" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G237" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="238" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B238" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C238" s="1">
+        <v>255773236807</v>
+      </c>
+      <c r="D238" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E238" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F238" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="G238" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="239" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B239" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C239" s="1">
+        <v>255746869672</v>
+      </c>
+      <c r="D239" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="E239" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F239" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="G239" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="240" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B240" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C240" s="1">
+        <v>255625529002</v>
+      </c>
+      <c r="D240" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="E240" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F240" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="G240" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="241" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B241" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C241" s="1">
+        <v>255625254819</v>
+      </c>
+      <c r="D241" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E241" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F241" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="G241" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="242" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B242" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C242" s="1">
+        <v>255715357258</v>
+      </c>
+      <c r="D242" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E242" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F242" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G242" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="243" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B243" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C243" s="1">
+        <v>255777893220</v>
+      </c>
+      <c r="D243" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E243" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F243" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="G243" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="244" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B244" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C244" s="1">
+        <v>255776262444</v>
+      </c>
+      <c r="D244" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E244" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F244" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G244" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="245" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B245" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C245" s="1">
+        <v>255717644744</v>
+      </c>
+      <c r="D245" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E245" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F245" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G245" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="246" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B246" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C246" s="1">
+        <v>255654230294</v>
+      </c>
+      <c r="D246" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E246" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F246" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G246" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="247" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B247" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C247" s="1">
+        <v>255777411887</v>
+      </c>
+      <c r="D247" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E247" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F247" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="G247" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="248" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B248" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C248" s="1">
+        <v>255683585634</v>
+      </c>
+      <c r="D248" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E248" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F248" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G248" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="249" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B249" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C249" s="1">
+        <v>255755940113</v>
+      </c>
+      <c r="D249" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E249" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F249" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="G249" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="250" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B250" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C250" s="1">
+        <v>255654592762</v>
+      </c>
+      <c r="D250" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E250" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F250" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="G250" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="251" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B251" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C251" s="1">
+        <v>255774195206</v>
+      </c>
+      <c r="D251" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E251" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F251" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="G251" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="252" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B252" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C252" s="1">
+        <v>255777873286</v>
+      </c>
+      <c r="D252" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E252" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F252" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G252" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="253" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B253" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C253" s="1">
+        <v>255767586809</v>
+      </c>
+      <c r="D253" s="1"/>
+      <c r="E253" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F253" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="G253" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="254" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B254" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C254" s="1">
+        <v>255772721854</v>
+      </c>
+      <c r="D254" s="1"/>
+      <c r="E254" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F254" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="G254" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="255" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B255" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C255" s="1">
+        <v>255777414823</v>
+      </c>
+      <c r="D255" s="1"/>
+      <c r="E255" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F255" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G255" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="256" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B256" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C256" s="1">
+        <v>255784682088</v>
+      </c>
+      <c r="D256" s="1"/>
+      <c r="E256" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F256" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="G256" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="259" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B259" s="1" t="s">
+        <v>1578</v>
+      </c>
+      <c r="C259" s="1">
+        <v>255763385936</v>
+      </c>
+      <c r="D259" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E259" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="F259" s="1" t="s">
+        <v>1579</v>
+      </c>
+      <c r="G259" s="1" t="s">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="260" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B260" s="1" t="s">
+        <v>1581</v>
+      </c>
+      <c r="C260" s="1">
+        <v>255767854653</v>
+      </c>
+      <c r="D260" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E260" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="F260" s="1" t="s">
+        <v>1582</v>
+      </c>
+      <c r="G260" s="1" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="261" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B261" s="1" t="s">
+        <v>1583</v>
+      </c>
+      <c r="C261" s="1">
+        <v>255656157044</v>
+      </c>
+      <c r="D261" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E261" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="F261" s="1" t="s">
+        <v>1584</v>
+      </c>
+      <c r="G261" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="262" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B262" s="1" t="s">
+        <v>1585</v>
+      </c>
+      <c r="C262" s="1">
+        <v>255774692088</v>
+      </c>
+      <c r="D262" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E262" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="F262" s="1" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G262" s="1" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="263" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B263" s="1" t="s">
+        <v>1587</v>
+      </c>
+      <c r="C263" s="1">
+        <v>255767171717</v>
+      </c>
+      <c r="D263" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E263" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="F263" s="1" t="s">
+        <v>1588</v>
+      </c>
+      <c r="G263" s="1" t="s">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="264" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B264" s="1" t="s">
+        <v>1590</v>
+      </c>
+      <c r="C264" s="1">
+        <v>777228297</v>
+      </c>
+      <c r="D264" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E264" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="F264" s="1" t="s">
+        <v>1591</v>
+      </c>
+      <c r="G264" s="1" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="265" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B265" s="1" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C265" s="1">
+        <v>255715518608</v>
+      </c>
+      <c r="D265" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E265" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="F265" s="1" t="s">
+        <v>1593</v>
+      </c>
+      <c r="G265" s="1" t="s">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="266" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B266" s="1" t="s">
+        <v>1595</v>
+      </c>
+      <c r="C266" s="1">
+        <v>255713030053</v>
+      </c>
+      <c r="D266" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E266" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="F266" s="1" t="s">
+        <v>1596</v>
+      </c>
+      <c r="G266" s="1" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="267" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B267" s="1" t="s">
+        <v>1597</v>
+      </c>
+      <c r="C267" s="1">
+        <v>201067307516</v>
+      </c>
+      <c r="D267" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E267" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="F267" s="1" t="s">
+        <v>1598</v>
+      </c>
+      <c r="G267" s="1" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="268" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B268" s="1" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C268" s="1">
+        <v>749484321</v>
+      </c>
+      <c r="D268" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E268" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="F268" s="1" t="s">
+        <v>1600</v>
+      </c>
+      <c r="G268" s="1" t="s">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="269" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B269" s="1" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C269" s="1">
+        <v>255612255396</v>
+      </c>
+      <c r="D269" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E269" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="F269" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="G269" s="1" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="270" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B270" s="1" t="s">
+        <v>1603</v>
+      </c>
+      <c r="C270" s="1">
+        <v>255654337391</v>
+      </c>
+      <c r="D270" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E270" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="F270" s="1" t="s">
+        <v>1604</v>
+      </c>
+      <c r="G270" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="271" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B271" s="1" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C271" s="1">
+        <v>255776298027</v>
+      </c>
+      <c r="D271" s="1"/>
+      <c r="E271" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="F271" s="1" t="s">
+        <v>1606</v>
+      </c>
+      <c r="G271" s="1" t="s">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="272" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B272" s="1" t="s">
+        <v>1608</v>
+      </c>
+      <c r="C272" s="1">
+        <v>255773807707</v>
+      </c>
+      <c r="D272" s="1"/>
+      <c r="E272" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="F272" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="G272" s="1"/>
+    </row>
+    <row r="273" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B273" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="C273" s="1"/>
+      <c r="D273" s="1"/>
+      <c r="E273" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="F273" s="1" t="s">
+        <v>1610</v>
+      </c>
+      <c r="G273" s="1"/>
+    </row>
+    <row r="274" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B274" s="1" t="s">
+        <v>1611</v>
+      </c>
+      <c r="C274" s="1">
+        <v>255784888888</v>
+      </c>
+      <c r="D274" s="1"/>
+      <c r="E274" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="F274" s="1" t="s">
+        <v>1612</v>
+      </c>
+      <c r="G274" s="1"/>
+    </row>
+    <row r="275" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B275" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="C275" s="1">
+        <v>255784888888</v>
+      </c>
+      <c r="D275" s="1"/>
+      <c r="E275" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="F275" s="1" t="s">
+        <v>1612</v>
+      </c>
+      <c r="G275" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="278" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B278" s="1" t="s">
+        <v>1614</v>
+      </c>
+      <c r="C278" s="1">
+        <v>255713113633</v>
+      </c>
+      <c r="D278" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E278" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F278" s="1" t="s">
+        <v>1616</v>
+      </c>
+      <c r="G278" s="1" t="s">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="279" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B279" s="1" t="s">
+        <v>1618</v>
+      </c>
+      <c r="C279" s="1">
+        <v>255756429122</v>
+      </c>
+      <c r="D279" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E279" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F279" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="G279" s="1" t="s">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="280" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B280" s="1" t="s">
+        <v>1620</v>
+      </c>
+      <c r="C280" s="1">
+        <v>255778800880</v>
+      </c>
+      <c r="D280" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E280" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F280" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="G280" s="1" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="281" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B281" s="1" t="s">
+        <v>1622</v>
+      </c>
+      <c r="C281" s="1">
+        <v>255777476088</v>
+      </c>
+      <c r="D281" s="1" t="s">
+        <v>1623</v>
+      </c>
+      <c r="E281" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F281" s="1" t="s">
+        <v>1624</v>
+      </c>
+      <c r="G281" s="1" t="s">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="282" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B282" s="1" t="s">
+        <v>1626</v>
+      </c>
+      <c r="C282" s="1">
+        <v>255773144446</v>
+      </c>
+      <c r="D282" s="1"/>
+      <c r="E282" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F282" s="1" t="s">
+        <v>1627</v>
+      </c>
+      <c r="G282" s="1" t="s">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="283" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B283" s="1" t="s">
+        <v>1629</v>
+      </c>
+      <c r="C283" s="1">
+        <v>255773792383</v>
+      </c>
+      <c r="D283" s="1"/>
+      <c r="E283" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F283" s="1" t="s">
+        <v>1630</v>
+      </c>
+      <c r="G283" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="284" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B284" s="1" t="s">
+        <v>1631</v>
+      </c>
+      <c r="C284" s="1">
+        <v>255774595600</v>
+      </c>
+      <c r="D284" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="E284" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F284" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G284" s="1" t="s">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="285" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B285" s="1" t="s">
+        <v>1633</v>
+      </c>
+      <c r="C285" s="1">
+        <v>255670872311</v>
+      </c>
+      <c r="D285" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="E285" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F285" s="1" t="s">
+        <v>1634</v>
+      </c>
+      <c r="G285" s="1" t="s">
+        <v>1635</v>
+      </c>
+    </row>
+    <row r="286" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B286" s="1" t="s">
+        <v>1636</v>
+      </c>
+      <c r="C286" s="1">
+        <v>255657091058</v>
+      </c>
+      <c r="D286" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E286" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F286" s="1" t="s">
+        <v>1637</v>
+      </c>
+      <c r="G286" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="287" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B287" s="1" t="s">
+        <v>1638</v>
+      </c>
+      <c r="C287" s="1">
+        <v>255777367576</v>
+      </c>
+      <c r="D287" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E287" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F287" s="1" t="s">
+        <v>1639</v>
+      </c>
+      <c r="G287" s="1"/>
+    </row>
+    <row r="288" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B288" s="1" t="s">
+        <v>1640</v>
+      </c>
+      <c r="C288" s="1">
+        <v>255759301122</v>
+      </c>
+      <c r="D288" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E288" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F288" s="1" t="s">
+        <v>1641</v>
+      </c>
+      <c r="G288" s="1" t="s">
+        <v>1642</v>
+      </c>
+    </row>
+    <row r="289" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B289" s="1" t="s">
+        <v>1643</v>
+      </c>
+      <c r="C289" s="1">
+        <v>255777429014</v>
+      </c>
+      <c r="D289" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="E289" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F289" s="1" t="s">
+        <v>1644</v>
+      </c>
+      <c r="G289" s="1" t="s">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="290" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B290" s="1" t="s">
+        <v>1645</v>
+      </c>
+      <c r="C290" s="1">
+        <v>255676349568</v>
+      </c>
+      <c r="D290" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="E290" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F290" s="1" t="s">
+        <v>1646</v>
+      </c>
+      <c r="G290" s="1" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="291" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B291" s="1" t="s">
+        <v>1647</v>
+      </c>
+      <c r="C291" s="1">
+        <v>255773870855</v>
+      </c>
+      <c r="D291" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E291" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F291" s="1" t="s">
+        <v>1648</v>
+      </c>
+      <c r="G291" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="292" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B292" s="1" t="s">
+        <v>1649</v>
+      </c>
+      <c r="C292" s="1">
+        <v>255676815155</v>
+      </c>
+      <c r="D292" s="1" t="s">
+        <v>1623</v>
+      </c>
+      <c r="E292" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F292" s="1" t="s">
+        <v>1650</v>
+      </c>
+      <c r="G292" s="1" t="s">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="293" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B293" s="1" t="s">
+        <v>1652</v>
+      </c>
+      <c r="C293" s="1">
+        <v>255716296405</v>
+      </c>
+      <c r="D293" s="1" t="s">
+        <v>1653</v>
+      </c>
+      <c r="E293" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F293" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="G293" s="1" t="s">
+        <v>1654</v>
+      </c>
+    </row>
+    <row r="294" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B294" s="1" t="s">
+        <v>1655</v>
+      </c>
+      <c r="C294" s="1">
+        <v>255777426126</v>
+      </c>
+      <c r="D294" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="E294" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F294" s="1" t="s">
+        <v>1656</v>
+      </c>
+      <c r="G294" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="295" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B295" s="1" t="s">
+        <v>1657</v>
+      </c>
+      <c r="C295" s="1">
+        <v>255777439999</v>
+      </c>
+      <c r="D295" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E295" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F295" s="1" t="s">
+        <v>1658</v>
+      </c>
+      <c r="G295" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="296" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B296" s="1" t="s">
+        <v>1659</v>
+      </c>
+      <c r="C296" s="1">
+        <v>255773887598</v>
+      </c>
+      <c r="D296" s="1" t="s">
+        <v>1321</v>
+      </c>
+      <c r="E296" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F296" s="1" t="s">
+        <v>1660</v>
+      </c>
+      <c r="G296" s="1" t="s">
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="297" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B297" s="1" t="s">
+        <v>1662</v>
+      </c>
+      <c r="C297" s="1">
+        <v>255625675712</v>
+      </c>
+      <c r="D297" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E297" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F297" s="1" t="s">
+        <v>1663</v>
+      </c>
+      <c r="G297" s="1" t="s">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="298" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B298" s="1" t="s">
+        <v>1665</v>
+      </c>
+      <c r="C298" s="1">
+        <v>255715304014</v>
+      </c>
+      <c r="D298" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E298" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F298" s="1" t="s">
+        <v>1666</v>
+      </c>
+      <c r="G298" s="1" t="s">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="299" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B299" s="1" t="s">
+        <v>1668</v>
+      </c>
+      <c r="C299" s="1">
+        <v>255788949496</v>
+      </c>
+      <c r="D299" s="1"/>
+      <c r="E299" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F299" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G299" s="1" t="s">
+        <v>1669</v>
+      </c>
+    </row>
+    <row r="300" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B300" s="1" t="s">
+        <v>1670</v>
+      </c>
+      <c r="C300" s="1">
+        <v>255777410801</v>
+      </c>
+      <c r="D300" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="E300" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F300" s="1" t="s">
+        <v>1671</v>
+      </c>
+      <c r="G300" s="1" t="s">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="301" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B301" s="1" t="s">
+        <v>1673</v>
+      </c>
+      <c r="C301" s="1">
+        <v>255653616719</v>
+      </c>
+      <c r="D301" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E301" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F301" s="1" t="s">
+        <v>1674</v>
+      </c>
+      <c r="G301" s="1" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="302" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B302" s="1" t="s">
+        <v>1676</v>
+      </c>
+      <c r="C302" s="1">
+        <v>255772767676</v>
+      </c>
+      <c r="D302" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E302" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F302" s="1" t="s">
+        <v>1677</v>
+      </c>
+      <c r="G302" s="1" t="s">
+        <v>1678</v>
+      </c>
+    </row>
+    <row r="303" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B303" s="1" t="s">
+        <v>1679</v>
+      </c>
+      <c r="C303" s="1">
+        <v>255773696269</v>
+      </c>
+      <c r="D303" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E303" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F303" s="1" t="s">
+        <v>1680</v>
+      </c>
+      <c r="G303" s="1" t="s">
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="304" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B304" s="1" t="s">
+        <v>1681</v>
+      </c>
+      <c r="C304" s="1">
+        <v>255675171562</v>
+      </c>
+      <c r="D304" s="1" t="s">
+        <v>1623</v>
+      </c>
+      <c r="E304" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F304" s="1" t="s">
+        <v>1682</v>
+      </c>
+      <c r="G304" s="1" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="305" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B305" s="1" t="s">
+        <v>1683</v>
+      </c>
+      <c r="C305" s="1">
+        <v>255655434345</v>
+      </c>
+      <c r="D305" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E305" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F305" s="1" t="s">
+        <v>1684</v>
+      </c>
+      <c r="G305" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="306" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B306" s="1" t="s">
+        <v>1685</v>
+      </c>
+      <c r="C306" s="1">
+        <v>255777020268</v>
+      </c>
+      <c r="D306" s="1" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E306" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F306" s="1"/>
+      <c r="G306" s="1" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="307" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B307" s="1" t="s">
+        <v>1686</v>
+      </c>
+      <c r="C307" s="1">
+        <v>255776663303</v>
+      </c>
+      <c r="D307" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E307" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F307" s="1" t="s">
+        <v>1687</v>
+      </c>
+      <c r="G307" s="1" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="308" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B308" s="1" t="s">
+        <v>1688</v>
+      </c>
+      <c r="C308" s="1">
+        <v>255679440336</v>
+      </c>
+      <c r="D308" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E308" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F308" s="1" t="s">
+        <v>1689</v>
+      </c>
+      <c r="G308" s="1" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="309" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B309" s="1" t="s">
+        <v>1690</v>
+      </c>
+      <c r="C309" s="1">
+        <v>255779127127</v>
+      </c>
+      <c r="D309" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E309" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F309" s="1" t="s">
+        <v>1691</v>
+      </c>
+      <c r="G309" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="312" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B312" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C312" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D312" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E312" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="F312" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="G312" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="H312" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="313" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B313" s="1" t="s">
+        <v>1692</v>
+      </c>
+      <c r="C313" s="1">
+        <v>255676117661</v>
+      </c>
+      <c r="D313" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E313" s="1" t="s">
+        <v>1693</v>
+      </c>
+      <c r="F313" s="1" t="s">
+        <v>1694</v>
+      </c>
+      <c r="G313" s="1"/>
+      <c r="H313" s="1"/>
+    </row>
+    <row r="314" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B314" s="1" t="s">
+        <v>1695</v>
+      </c>
+      <c r="C314" s="1">
+        <v>18043806802</v>
+      </c>
+      <c r="D314" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E314" s="1" t="s">
+        <v>1693</v>
+      </c>
+      <c r="F314" s="1" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G314" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="H314" s="1"/>
+    </row>
+    <row r="315" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B315" s="1" t="s">
+        <v>1697</v>
+      </c>
+      <c r="C315" s="1">
+        <v>765919299</v>
+      </c>
+      <c r="D315" s="1" t="s">
+        <v>1698</v>
+      </c>
+      <c r="E315" s="1" t="s">
+        <v>1693</v>
+      </c>
+      <c r="F315" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="G315" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="H315" s="1"/>
+    </row>
+    <row r="316" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B316" s="1" t="s">
+        <v>1699</v>
+      </c>
+      <c r="C316" s="1" t="s">
+        <v>1700</v>
+      </c>
+      <c r="D316" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E316" s="1" t="s">
+        <v>1693</v>
+      </c>
+      <c r="F316" s="1" t="s">
+        <v>1701</v>
+      </c>
+      <c r="G316" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="H316" s="1"/>
+    </row>
+    <row r="317" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B317" s="1" t="s">
+        <v>1702</v>
+      </c>
+      <c r="C317" s="1">
+        <v>447539362498</v>
+      </c>
+      <c r="D317" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E317" s="1" t="s">
+        <v>1693</v>
+      </c>
+      <c r="F317" s="1" t="s">
+        <v>1703</v>
+      </c>
+      <c r="G317" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="H317" s="1" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="318" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B318" s="1" t="s">
+        <v>1704</v>
+      </c>
+      <c r="C318" s="1">
+        <v>255776111905</v>
+      </c>
+      <c r="D318" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E318" s="1" t="s">
+        <v>1693</v>
+      </c>
+      <c r="F318" s="1" t="s">
+        <v>1705</v>
+      </c>
+      <c r="G318" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="H318" s="1"/>
+    </row>
+    <row r="319" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B319" s="1" t="s">
+        <v>1706</v>
+      </c>
+      <c r="C319" s="1">
+        <v>255657159121</v>
+      </c>
+      <c r="D319" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="E319" s="1" t="s">
+        <v>1693</v>
+      </c>
+      <c r="F319" s="1" t="s">
+        <v>1707</v>
+      </c>
+      <c r="G319" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="H319" s="1"/>
+    </row>
+    <row r="320" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B320" s="1" t="s">
+        <v>1708</v>
+      </c>
+      <c r="C320" s="1">
+        <v>255776143613</v>
+      </c>
+      <c r="D320" s="1" t="s">
+        <v>1709</v>
+      </c>
+      <c r="E320" s="1" t="s">
+        <v>1693</v>
+      </c>
+      <c r="F320" s="1" t="s">
+        <v>1710</v>
+      </c>
+      <c r="G320" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="H320" s="1" t="s">
+        <v>1711</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{99ef9a43-ff34-4715-a5f5-dfd82916d644}" enabled="1" method="Standard" siteId="{68792612-0f0e-46cb-b16a-fcb82fd80cb1}" contentBits="2" removed="0"/>
